--- a/Design-Files/PowerCutMonitor-v1.1 (Contactless Version)/BOM/JLCPCB_BOM_PowerCutMonitor-v1.1.xlsx
+++ b/Design-Files/PowerCutMonitor-v1.1 (Contactless Version)/BOM/JLCPCB_BOM_PowerCutMonitor-v1.1.xlsx
@@ -168,7 +168,7 @@
     <t>Q3</t>
   </si>
   <si>
-    <t>R1, R2, R3</t>
+    <t>R1, R2, R3, R15</t>
   </si>
   <si>
     <t>R4, R5, R7</t>
@@ -189,7 +189,7 @@
     <t>SW1</t>
   </si>
   <si>
-    <t>SW2, SW3</t>
+    <t>SW2, SW3, SW4</t>
   </si>
   <si>
     <t>U1</t>

--- a/Design-Files/PowerCutMonitor-v1.1 (Contactless Version)/BOM/JLCPCB_BOM_PowerCutMonitor-v1.1.xlsx
+++ b/Design-Files/PowerCutMonitor-v1.1 (Contactless Version)/BOM/JLCPCB_BOM_PowerCutMonitor-v1.1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\davetetlow-PowerCutMonitor\Design-Files\PowerCutMonitor-v1.1 (Contactless Version)\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iftikhar Ahmed\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="120">
   <si>
     <t>Comment</t>
   </si>
@@ -66,6 +66,9 @@
     <t>Emerald</t>
   </si>
   <si>
+    <t>A-SC6302R6AGHC-A03-2T</t>
+  </si>
+  <si>
     <t>AO3407</t>
   </si>
   <si>
@@ -75,6 +78,9 @@
     <t>MMBT3904M</t>
   </si>
   <si>
+    <t>AO3400A</t>
+  </si>
+  <si>
     <t>10K</t>
   </si>
   <si>
@@ -93,6 +99,9 @@
     <t>100K</t>
   </si>
   <si>
+    <t>680R</t>
+  </si>
+  <si>
     <t>SS-12D10L9</t>
   </si>
   <si>
@@ -159,6 +168,9 @@
     <t>LED1</t>
   </si>
   <si>
+    <t>LED2</t>
+  </si>
+  <si>
     <t>Q1</t>
   </si>
   <si>
@@ -168,6 +180,9 @@
     <t>Q3</t>
   </si>
   <si>
+    <t>Q5, Q6</t>
+  </si>
+  <si>
     <t>R1, R2, R3, R15</t>
   </si>
   <si>
@@ -186,6 +201,9 @@
     <t>R12, R13, R14</t>
   </si>
   <si>
+    <t>R16, R17, R18, R19</t>
+  </si>
+  <si>
     <t>SW1</t>
   </si>
   <si>
@@ -246,6 +264,9 @@
     <t>SOT-723</t>
   </si>
   <si>
+    <t>sot-23</t>
+  </si>
+  <si>
     <t>Res-0402</t>
   </si>
   <si>
@@ -306,6 +327,9 @@
     <t>C87326</t>
   </si>
   <si>
+    <t>C5355456</t>
+  </si>
+  <si>
     <t>C181093</t>
   </si>
   <si>
@@ -315,6 +339,9 @@
     <t>C2923360</t>
   </si>
   <si>
+    <t>C344010</t>
+  </si>
+  <si>
     <t>C60490</t>
   </si>
   <si>
@@ -349,6 +376,9 @@
   </si>
   <si>
     <t>C32346</t>
+  </si>
+  <si>
+    <t>C137948</t>
   </si>
 </sst>
 </file>
@@ -794,7 +824,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -808,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -822,13 +852,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -836,13 +866,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -850,13 +880,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -864,13 +894,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -878,13 +908,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -892,13 +922,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -906,13 +936,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -920,13 +950,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -934,13 +964,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -948,13 +978,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -962,13 +992,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -976,13 +1006,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -990,13 +1020,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1004,13 +1034,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1018,27 +1048,27 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1046,13 +1076,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1060,13 +1090,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1074,13 +1104,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1088,13 +1118,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1102,13 +1132,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1116,13 +1146,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1130,13 +1160,13 @@
         <v>22</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1144,13 +1174,13 @@
         <v>23</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1158,13 +1188,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1172,27 +1202,27 @@
         <v>25</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1200,13 +1230,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1214,27 +1244,69 @@
         <v>28</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>109</v>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/Design-Files/PowerCutMonitor-v1.1 (Contactless Version)/BOM/JLCPCB_BOM_PowerCutMonitor-v1.1.xlsx
+++ b/Design-Files/PowerCutMonitor-v1.1 (Contactless Version)/BOM/JLCPCB_BOM_PowerCutMonitor-v1.1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iftikhar Ahmed\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\davetetlow-PowerCutMonitor\Design-Files\PowerCutMonitor-v1.1 (Contactless Version)\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A78B06-3704-4237-805A-461886794E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -114,9 +115,6 @@
     <t>AP63203WU-7</t>
   </si>
   <si>
-    <t>CD40175BE</t>
-  </si>
-  <si>
     <t>Q13FC13500004</t>
   </si>
   <si>
@@ -273,9 +271,6 @@
     <t>TSOT-23-6</t>
   </si>
   <si>
-    <t>PDIP-16</t>
-  </si>
-  <si>
     <t>SMD3215-2P</t>
   </si>
   <si>
@@ -372,19 +367,25 @@
     <t>C780769</t>
   </si>
   <si>
-    <t>C105634</t>
-  </si>
-  <si>
     <t>C32346</t>
   </si>
   <si>
     <t>C137948</t>
+  </si>
+  <si>
+    <t>C32710674</t>
+  </si>
+  <si>
+    <t>CD4017BE(LX)</t>
+  </si>
+  <si>
+    <t>DIP-16</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -822,7 +823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -838,13 +839,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -852,13 +853,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -866,13 +867,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -880,13 +881,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -894,13 +895,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -908,13 +909,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -922,13 +923,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -936,13 +937,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -950,13 +951,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -964,13 +965,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -978,13 +979,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -992,13 +993,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1006,13 +1007,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1020,13 +1021,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1034,13 +1035,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1048,13 +1049,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -1062,13 +1063,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1076,13 +1077,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1090,13 +1091,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1104,13 +1105,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1118,13 +1119,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1132,13 +1133,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1146,13 +1147,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1160,13 +1161,13 @@
         <v>22</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1174,13 +1175,13 @@
         <v>23</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1188,13 +1189,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1202,13 +1203,13 @@
         <v>25</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1216,13 +1217,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1230,13 +1231,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1244,13 +1245,13 @@
         <v>28</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -1258,13 +1259,13 @@
         <v>29</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1272,24 +1273,24 @@
         <v>30</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>117</v>
@@ -1297,16 +1298,16 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/Design-Files/PowerCutMonitor-v1.1 (Contactless Version)/BOM/JLCPCB_BOM_PowerCutMonitor-v1.1.xlsx
+++ b/Design-Files/PowerCutMonitor-v1.1 (Contactless Version)/BOM/JLCPCB_BOM_PowerCutMonitor-v1.1.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\davetetlow-PowerCutMonitor\Design-Files\PowerCutMonitor-v1.1 (Contactless Version)\BOM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6076395-2FA1-4A00-A7CD-D7EF31A8939B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -27,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="123">
   <si>
     <t>Comment</t>
   </si>
@@ -128,15 +132,9 @@
     <t>C1517827</t>
   </si>
   <si>
-    <t>33uF</t>
-  </si>
-  <si>
     <t>C15</t>
   </si>
   <si>
-    <t>C7202</t>
-  </si>
-  <si>
     <t>MM3Z3V3B</t>
   </si>
   <si>
@@ -284,9 +282,6 @@
     <t>1K</t>
   </si>
   <si>
-    <t>R5, R7</t>
-  </si>
-  <si>
     <t>C106235</t>
   </si>
   <si>
@@ -302,9 +297,6 @@
     <t>4.7K</t>
   </si>
   <si>
-    <t>R8</t>
-  </si>
-  <si>
     <t>C105871</t>
   </si>
   <si>
@@ -320,9 +312,6 @@
     <t>100K</t>
   </si>
   <si>
-    <t>R12, R13, R14</t>
-  </si>
-  <si>
     <t>C60491</t>
   </si>
   <si>
@@ -335,15 +324,6 @@
     <t>C137948</t>
   </si>
   <si>
-    <t>0R</t>
-  </si>
-  <si>
-    <t>R20, R21, R22</t>
-  </si>
-  <si>
-    <t>C106231</t>
-  </si>
-  <si>
     <t>SS-12D10L9</t>
   </si>
   <si>
@@ -405,19 +385,28 @@
   </si>
   <si>
     <t>C32346</t>
+  </si>
+  <si>
+    <t>47uF</t>
+  </si>
+  <si>
+    <t>C308881</t>
+  </si>
+  <si>
+    <t>R5, R7. R10</t>
+  </si>
+  <si>
+    <t>R8, R12</t>
+  </si>
+  <si>
+    <t>R13, R14</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -439,152 +428,8 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -603,194 +448,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="15">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -872,251 +531,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1142,67 +559,23 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="0003A4CB"/>
-      <color rgb="002CD0B2"/>
+      <color rgb="FF03A4CB"/>
+      <color rgb="FF2CD0B2"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1460,22 +833,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.7142857142857" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="19.2857142857143" customWidth="1"/>
-    <col min="4" max="4" width="26.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="4" max="4" width="26.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:4">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1603,385 +977,370 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="D11" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="D15" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="5" t="s">
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="B17" s="6" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="17" ht="24" spans="1:4">
-      <c r="A17" s="6" t="s">
+      <c r="C17" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="D19" s="6" t="s">
         <v>66</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="D20" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="D21" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B29" s="6" t="s">
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D29" s="6" t="s">
+      <c r="B31" s="4" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="4" t="s">
+      <c r="C31" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="4" t="s">
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D30" s="4" t="s">
+      <c r="B32" s="6" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="6" t="s">
+      <c r="C32" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B31" s="6" t="s">
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D31" s="6" t="s">
+      <c r="B33" s="4" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="4" t="s">
+      <c r="C33" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="D33" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D32" s="4" t="s">
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="6" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="33" ht="24" spans="1:4">
-      <c r="A33" s="6" t="s">
+      <c r="B34" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="C34" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="D33" s="6" t="s">
+      <c r="D34" s="6" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="4" t="s">
+    <row r="35" spans="1:4">
+      <c r="A35" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B35" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C35" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D35" s="4" t="s">
         <v>117</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>125</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Design-Files/PowerCutMonitor-v1.1 (Contactless Version)/BOM/JLCPCB_BOM_PowerCutMonitor-v1.1.xlsx
+++ b/Design-Files/PowerCutMonitor-v1.1 (Contactless Version)/BOM/JLCPCB_BOM_PowerCutMonitor-v1.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\davetetlow-PowerCutMonitor\Design-Files\PowerCutMonitor-v1.1 (Contactless Version)\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6076395-2FA1-4A00-A7CD-D7EF31A8939B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E61A0E5-EDD9-4B49-9582-7F92423A710F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="126">
   <si>
     <t>Comment</t>
   </si>
@@ -400,6 +400,15 @@
   </si>
   <si>
     <t>R13, R14</t>
+  </si>
+  <si>
+    <t>0R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R11 </t>
+  </si>
+  <si>
+    <t>C106231</t>
   </si>
 </sst>
 </file>
@@ -840,13 +849,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:D36"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="26.5546875" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1073,7 +1082,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" ht="24">
       <c r="A17" s="6" t="s">
         <v>56</v>
       </c>
@@ -1283,7 +1292,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" ht="24">
       <c r="A32" s="6" t="s">
         <v>103</v>
       </c>
@@ -1337,6 +1346,20 @@
       </c>
       <c r="D35" s="4" t="s">
         <v>117</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
